--- a/data/2026-2027/Wellness.xlsx
+++ b/data/2026-2027/Wellness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A23D9A-819F-FA4F-A325-05B6CEAC1A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6A8540-A77A-F742-81CD-3AD2437BB334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="109">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -354,6 +354,15 @@
   </si>
   <si>
     <t>Sensation de cheville verrouillé à droite </t>
+  </si>
+  <si>
+    <t>Tibia </t>
+  </si>
+  <si>
+    <t>Pied </t>
+  </si>
+  <si>
+    <t>Dos/cervicale</t>
   </si>
 </sst>
 </file>
@@ -740,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:J668"/>
+  <dimension ref="A1:J708"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -19490,7 +19499,7 @@
         <v>9</v>
       </c>
       <c r="I643">
-        <f t="shared" ref="I643:I668" si="10">C643*D643</f>
+        <f t="shared" ref="I643:I706" si="10">C643*D643</f>
         <v>480</v>
       </c>
     </row>
@@ -20206,6 +20215,1144 @@
       <c r="I668">
         <f t="shared" si="10"/>
         <v>420</v>
+      </c>
+    </row>
+    <row r="669" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A669" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C669" s="1">
+        <v>60</v>
+      </c>
+      <c r="D669" s="1">
+        <v>4</v>
+      </c>
+      <c r="E669" s="1">
+        <v>6</v>
+      </c>
+      <c r="F669" s="1">
+        <v>7</v>
+      </c>
+      <c r="G669" s="2"/>
+      <c r="H669" s="1">
+        <v>4</v>
+      </c>
+      <c r="I669">
+        <f t="shared" si="10"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="670" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A670" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C670" s="1">
+        <v>60</v>
+      </c>
+      <c r="D670" s="1">
+        <v>3</v>
+      </c>
+      <c r="E670" s="1">
+        <v>3</v>
+      </c>
+      <c r="F670" s="1">
+        <v>1</v>
+      </c>
+      <c r="G670" s="2"/>
+      <c r="H670" s="1">
+        <v>7</v>
+      </c>
+      <c r="I670">
+        <f t="shared" si="10"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="671" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A671" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C671" s="1">
+        <v>60</v>
+      </c>
+      <c r="D671" s="1">
+        <v>3</v>
+      </c>
+      <c r="E671" s="1">
+        <v>2</v>
+      </c>
+      <c r="F671" s="1">
+        <v>0</v>
+      </c>
+      <c r="G671" s="2"/>
+      <c r="H671" s="1">
+        <v>7</v>
+      </c>
+      <c r="I671">
+        <f t="shared" si="10"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="672" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A672" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C672" s="1">
+        <v>60</v>
+      </c>
+      <c r="D672" s="1">
+        <v>4</v>
+      </c>
+      <c r="E672" s="1">
+        <v>2</v>
+      </c>
+      <c r="F672" s="1">
+        <v>2</v>
+      </c>
+      <c r="G672" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H672" s="1">
+        <v>6</v>
+      </c>
+      <c r="I672">
+        <f t="shared" si="10"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="673" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A673" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C673" s="1">
+        <v>60</v>
+      </c>
+      <c r="D673" s="1">
+        <v>5</v>
+      </c>
+      <c r="E673" s="1">
+        <v>5</v>
+      </c>
+      <c r="F673" s="1">
+        <v>0</v>
+      </c>
+      <c r="G673" s="2"/>
+      <c r="H673" s="1">
+        <v>7</v>
+      </c>
+      <c r="I673">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="674" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A674" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C674" s="1">
+        <v>60</v>
+      </c>
+      <c r="D674" s="1">
+        <v>4</v>
+      </c>
+      <c r="E674" s="1">
+        <v>3</v>
+      </c>
+      <c r="F674" s="1">
+        <v>0</v>
+      </c>
+      <c r="G674" s="2"/>
+      <c r="H674" s="1">
+        <v>6</v>
+      </c>
+      <c r="I674">
+        <f t="shared" si="10"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="675" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A675" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C675" s="1">
+        <v>60</v>
+      </c>
+      <c r="D675" s="1">
+        <v>5</v>
+      </c>
+      <c r="E675" s="1">
+        <v>5</v>
+      </c>
+      <c r="F675" s="1">
+        <v>0</v>
+      </c>
+      <c r="G675" s="2"/>
+      <c r="H675" s="1">
+        <v>7</v>
+      </c>
+      <c r="I675">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="676" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A676" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C676" s="1">
+        <v>60</v>
+      </c>
+      <c r="D676" s="1">
+        <v>3</v>
+      </c>
+      <c r="E676" s="1">
+        <v>3</v>
+      </c>
+      <c r="F676" s="1">
+        <v>0</v>
+      </c>
+      <c r="G676" s="2"/>
+      <c r="H676" s="1">
+        <v>5</v>
+      </c>
+      <c r="I676">
+        <f t="shared" si="10"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="677" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A677" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C677" s="1">
+        <v>60</v>
+      </c>
+      <c r="D677" s="1">
+        <v>4</v>
+      </c>
+      <c r="E677" s="1">
+        <v>5</v>
+      </c>
+      <c r="F677" s="1">
+        <v>4</v>
+      </c>
+      <c r="G677" s="2"/>
+      <c r="H677" s="1">
+        <v>6</v>
+      </c>
+      <c r="I677">
+        <f t="shared" si="10"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="678" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A678" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C678" s="1">
+        <v>60</v>
+      </c>
+      <c r="D678" s="1">
+        <v>4</v>
+      </c>
+      <c r="E678" s="1">
+        <v>4</v>
+      </c>
+      <c r="F678" s="1">
+        <v>0</v>
+      </c>
+      <c r="G678" s="2"/>
+      <c r="H678" s="1">
+        <v>6</v>
+      </c>
+      <c r="I678">
+        <f t="shared" si="10"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="679" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A679" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C679" s="1">
+        <v>60</v>
+      </c>
+      <c r="D679" s="1">
+        <v>5</v>
+      </c>
+      <c r="E679" s="1">
+        <v>5</v>
+      </c>
+      <c r="F679" s="1">
+        <v>5</v>
+      </c>
+      <c r="G679" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H679" s="1">
+        <v>8</v>
+      </c>
+      <c r="I679">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="680" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A680" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C680" s="1">
+        <v>60</v>
+      </c>
+      <c r="D680" s="1">
+        <v>7</v>
+      </c>
+      <c r="E680" s="1">
+        <v>6</v>
+      </c>
+      <c r="F680" s="1">
+        <v>0</v>
+      </c>
+      <c r="G680" s="2"/>
+      <c r="H680" s="1">
+        <v>8</v>
+      </c>
+      <c r="I680">
+        <f t="shared" si="10"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="681" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A681" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C681" s="1">
+        <v>60</v>
+      </c>
+      <c r="D681" s="1">
+        <v>2</v>
+      </c>
+      <c r="E681" s="1">
+        <v>0</v>
+      </c>
+      <c r="F681" s="1">
+        <v>2</v>
+      </c>
+      <c r="G681" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H681" s="1">
+        <v>10</v>
+      </c>
+      <c r="I681">
+        <f t="shared" si="10"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="682" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A682" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C682" s="1">
+        <v>50</v>
+      </c>
+      <c r="D682" s="1">
+        <v>7</v>
+      </c>
+      <c r="E682" s="1">
+        <v>5</v>
+      </c>
+      <c r="F682" s="1">
+        <v>0</v>
+      </c>
+      <c r="G682" s="2"/>
+      <c r="H682" s="1">
+        <v>8</v>
+      </c>
+      <c r="I682">
+        <f t="shared" si="10"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="683" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A683" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C683" s="1">
+        <v>50</v>
+      </c>
+      <c r="D683" s="1">
+        <v>3</v>
+      </c>
+      <c r="E683" s="1">
+        <v>0</v>
+      </c>
+      <c r="F683" s="1">
+        <v>0</v>
+      </c>
+      <c r="G683" s="2"/>
+      <c r="H683" s="1">
+        <v>10</v>
+      </c>
+      <c r="I683">
+        <f t="shared" si="10"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="684" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A684" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C684" s="1">
+        <v>50</v>
+      </c>
+      <c r="D684" s="1">
+        <v>7</v>
+      </c>
+      <c r="E684" s="1">
+        <v>7</v>
+      </c>
+      <c r="F684" s="1">
+        <v>0</v>
+      </c>
+      <c r="G684" s="2"/>
+      <c r="H684" s="1">
+        <v>7</v>
+      </c>
+      <c r="I684">
+        <f t="shared" si="10"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="685" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A685" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C685" s="1">
+        <v>50</v>
+      </c>
+      <c r="D685" s="1">
+        <v>4</v>
+      </c>
+      <c r="E685" s="1">
+        <v>3</v>
+      </c>
+      <c r="F685" s="1">
+        <v>2</v>
+      </c>
+      <c r="G685" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H685" s="1">
+        <v>7</v>
+      </c>
+      <c r="I685">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="686" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A686" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C686" s="1">
+        <v>50</v>
+      </c>
+      <c r="D686" s="1">
+        <v>4</v>
+      </c>
+      <c r="E686" s="1">
+        <v>0</v>
+      </c>
+      <c r="F686" s="1">
+        <v>0</v>
+      </c>
+      <c r="G686" s="2"/>
+      <c r="H686" s="1">
+        <v>6</v>
+      </c>
+      <c r="I686">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="687" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A687" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C687" s="1">
+        <v>50</v>
+      </c>
+      <c r="D687" s="1">
+        <v>5</v>
+      </c>
+      <c r="E687" s="1">
+        <v>3</v>
+      </c>
+      <c r="F687" s="1">
+        <v>0</v>
+      </c>
+      <c r="G687" s="2"/>
+      <c r="H687" s="1">
+        <v>8</v>
+      </c>
+      <c r="I687">
+        <f t="shared" si="10"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="688" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A688" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C688" s="1">
+        <v>50</v>
+      </c>
+      <c r="D688" s="1">
+        <v>6</v>
+      </c>
+      <c r="E688" s="1">
+        <v>4</v>
+      </c>
+      <c r="F688" s="1">
+        <v>0</v>
+      </c>
+      <c r="G688" s="2"/>
+      <c r="H688" s="1">
+        <v>7</v>
+      </c>
+      <c r="I688">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="689" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A689" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C689" s="1">
+        <v>50</v>
+      </c>
+      <c r="D689" s="1">
+        <v>4</v>
+      </c>
+      <c r="E689" s="1">
+        <v>5</v>
+      </c>
+      <c r="F689" s="1">
+        <v>6</v>
+      </c>
+      <c r="G689" s="2"/>
+      <c r="H689" s="1">
+        <v>7</v>
+      </c>
+      <c r="I689">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="690" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A690" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C690" s="1">
+        <v>50</v>
+      </c>
+      <c r="D690" s="1">
+        <v>3</v>
+      </c>
+      <c r="E690" s="1">
+        <v>4</v>
+      </c>
+      <c r="F690" s="1">
+        <v>4</v>
+      </c>
+      <c r="G690" s="2"/>
+      <c r="H690" s="1">
+        <v>10</v>
+      </c>
+      <c r="I690">
+        <f t="shared" si="10"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="691" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A691" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C691" s="1">
+        <v>50</v>
+      </c>
+      <c r="D691" s="1">
+        <v>6</v>
+      </c>
+      <c r="E691" s="1">
+        <v>6</v>
+      </c>
+      <c r="F691" s="1">
+        <v>6</v>
+      </c>
+      <c r="G691" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H691" s="1">
+        <v>8</v>
+      </c>
+      <c r="I691">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="692" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A692" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C692" s="1">
+        <v>50</v>
+      </c>
+      <c r="D692" s="1">
+        <v>3</v>
+      </c>
+      <c r="E692" s="1">
+        <v>3</v>
+      </c>
+      <c r="F692" s="1">
+        <v>1</v>
+      </c>
+      <c r="G692" s="2"/>
+      <c r="H692" s="1">
+        <v>7</v>
+      </c>
+      <c r="I692">
+        <f t="shared" si="10"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="693" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A693" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C693" s="1">
+        <v>50</v>
+      </c>
+      <c r="D693" s="1">
+        <v>2</v>
+      </c>
+      <c r="E693" s="1">
+        <v>2</v>
+      </c>
+      <c r="F693" s="1">
+        <v>0</v>
+      </c>
+      <c r="G693" s="2"/>
+      <c r="H693" s="1">
+        <v>8</v>
+      </c>
+      <c r="I693">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="694" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A694" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C694" s="1">
+        <v>50</v>
+      </c>
+      <c r="D694" s="1">
+        <v>4</v>
+      </c>
+      <c r="E694" s="1">
+        <v>1</v>
+      </c>
+      <c r="F694" s="1">
+        <v>3</v>
+      </c>
+      <c r="G694" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H694" s="1">
+        <v>7</v>
+      </c>
+      <c r="I694">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="695" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A695" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C695" s="1">
+        <v>50</v>
+      </c>
+      <c r="D695" s="1">
+        <v>6</v>
+      </c>
+      <c r="E695" s="1">
+        <v>5</v>
+      </c>
+      <c r="F695" s="1">
+        <v>2</v>
+      </c>
+      <c r="G695" s="2"/>
+      <c r="H695" s="1">
+        <v>5</v>
+      </c>
+      <c r="I695">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="696" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A696" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C696" s="1">
+        <v>50</v>
+      </c>
+      <c r="D696" s="1">
+        <v>7</v>
+      </c>
+      <c r="E696" s="1">
+        <v>9</v>
+      </c>
+      <c r="F696" s="1">
+        <v>0</v>
+      </c>
+      <c r="G696" s="2"/>
+      <c r="H696" s="1">
+        <v>8</v>
+      </c>
+      <c r="I696">
+        <f t="shared" si="10"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="697" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A697" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C697" s="1">
+        <v>50</v>
+      </c>
+      <c r="D697" s="1">
+        <v>5</v>
+      </c>
+      <c r="E697" s="1">
+        <v>5</v>
+      </c>
+      <c r="F697" s="1">
+        <v>0</v>
+      </c>
+      <c r="G697" s="2"/>
+      <c r="H697" s="1">
+        <v>0</v>
+      </c>
+      <c r="I697">
+        <f t="shared" si="10"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="698" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A698" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C698" s="1">
+        <v>50</v>
+      </c>
+      <c r="D698" s="1">
+        <v>4</v>
+      </c>
+      <c r="E698" s="1">
+        <v>0</v>
+      </c>
+      <c r="F698" s="1">
+        <v>0</v>
+      </c>
+      <c r="G698" s="2"/>
+      <c r="H698" s="1">
+        <v>10</v>
+      </c>
+      <c r="I698">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="699" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A699" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C699" s="1">
+        <v>50</v>
+      </c>
+      <c r="D699" s="1">
+        <v>6</v>
+      </c>
+      <c r="E699" s="1">
+        <v>4</v>
+      </c>
+      <c r="F699" s="1">
+        <v>4</v>
+      </c>
+      <c r="G699" s="2"/>
+      <c r="H699" s="1">
+        <v>2</v>
+      </c>
+      <c r="I699">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="700" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A700" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C700" s="1">
+        <v>50</v>
+      </c>
+      <c r="D700" s="1">
+        <v>1</v>
+      </c>
+      <c r="E700" s="1">
+        <v>0</v>
+      </c>
+      <c r="F700" s="1">
+        <v>6</v>
+      </c>
+      <c r="G700" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H700" s="1">
+        <v>3</v>
+      </c>
+      <c r="I700">
+        <f t="shared" si="10"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="701" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A701" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C701" s="1">
+        <v>50</v>
+      </c>
+      <c r="D701" s="1">
+        <v>4</v>
+      </c>
+      <c r="E701" s="1">
+        <v>3</v>
+      </c>
+      <c r="F701" s="1">
+        <v>0</v>
+      </c>
+      <c r="G701" s="2"/>
+      <c r="H701" s="1">
+        <v>7</v>
+      </c>
+      <c r="I701">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="702" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A702" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C702" s="1">
+        <v>50</v>
+      </c>
+      <c r="D702" s="1">
+        <v>7</v>
+      </c>
+      <c r="E702" s="1">
+        <v>5</v>
+      </c>
+      <c r="F702" s="1">
+        <v>5</v>
+      </c>
+      <c r="G702" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H702" s="1">
+        <v>10</v>
+      </c>
+      <c r="I702">
+        <f t="shared" si="10"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="703" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A703" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C703" s="1">
+        <v>50</v>
+      </c>
+      <c r="D703" s="1">
+        <v>6</v>
+      </c>
+      <c r="E703" s="1">
+        <v>6</v>
+      </c>
+      <c r="F703" s="1">
+        <v>3</v>
+      </c>
+      <c r="G703" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H703" s="1">
+        <v>7</v>
+      </c>
+      <c r="I703">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="704" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A704" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C704" s="1">
+        <v>50</v>
+      </c>
+      <c r="D704" s="1">
+        <v>5</v>
+      </c>
+      <c r="E704" s="1">
+        <v>4</v>
+      </c>
+      <c r="F704" s="1">
+        <v>6</v>
+      </c>
+      <c r="G704" s="2"/>
+      <c r="H704" s="1">
+        <v>9</v>
+      </c>
+      <c r="I704">
+        <f t="shared" si="10"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="705" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A705" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C705" s="1">
+        <v>50</v>
+      </c>
+      <c r="D705" s="1">
+        <v>4</v>
+      </c>
+      <c r="E705" s="1">
+        <v>2</v>
+      </c>
+      <c r="F705" s="1">
+        <v>2</v>
+      </c>
+      <c r="G705" s="2"/>
+      <c r="H705" s="1">
+        <v>6</v>
+      </c>
+      <c r="I705">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="706" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A706" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C706" s="1">
+        <v>50</v>
+      </c>
+      <c r="D706" s="1">
+        <v>6</v>
+      </c>
+      <c r="E706" s="1">
+        <v>4</v>
+      </c>
+      <c r="F706" s="1">
+        <v>0</v>
+      </c>
+      <c r="G706" s="2"/>
+      <c r="H706" s="1">
+        <v>8</v>
+      </c>
+      <c r="I706">
+        <f t="shared" si="10"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="707" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A707" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C707" s="1">
+        <v>50</v>
+      </c>
+      <c r="D707" s="1">
+        <v>2</v>
+      </c>
+      <c r="E707" s="1">
+        <v>1</v>
+      </c>
+      <c r="F707" s="1">
+        <v>1</v>
+      </c>
+      <c r="G707" s="2"/>
+      <c r="H707" s="1">
+        <v>7</v>
+      </c>
+      <c r="I707">
+        <f t="shared" ref="I707:I708" si="11">C707*D707</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="708" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A708" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C708" s="1">
+        <v>50</v>
+      </c>
+      <c r="D708" s="1">
+        <v>6</v>
+      </c>
+      <c r="E708" s="1">
+        <v>5</v>
+      </c>
+      <c r="F708" s="1">
+        <v>0</v>
+      </c>
+      <c r="G708" s="2"/>
+      <c r="H708" s="1">
+        <v>6</v>
+      </c>
+      <c r="I708">
+        <f t="shared" si="11"/>
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Wellness.xlsx
+++ b/data/2026-2027/Wellness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6A8540-A77A-F742-81CD-3AD2437BB334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D449821D-AA8F-E548-8A0B-6EC7B6D5530A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="111">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -363,6 +363,12 @@
   </si>
   <si>
     <t>Dos/cervicale</t>
+  </si>
+  <si>
+    <t>Pied</t>
+  </si>
+  <si>
+    <t>Ampoule</t>
   </si>
 </sst>
 </file>
@@ -749,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:J708"/>
+  <dimension ref="A1:J738"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -21323,7 +21329,7 @@
         <v>7</v>
       </c>
       <c r="I707">
-        <f t="shared" ref="I707:I708" si="11">C707*D707</f>
+        <f t="shared" ref="I707:I738" si="11">C707*D707</f>
         <v>100</v>
       </c>
     </row>
@@ -21353,6 +21359,856 @@
       <c r="I708">
         <f t="shared" si="11"/>
         <v>300</v>
+      </c>
+    </row>
+    <row r="709" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A709" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C709" s="1">
+        <v>60</v>
+      </c>
+      <c r="D709" s="1">
+        <v>8</v>
+      </c>
+      <c r="E709" s="1">
+        <v>8</v>
+      </c>
+      <c r="F709" s="1">
+        <v>0</v>
+      </c>
+      <c r="G709" s="2"/>
+      <c r="H709" s="1">
+        <v>7</v>
+      </c>
+      <c r="I709">
+        <f t="shared" si="11"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="710" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A710" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C710" s="1">
+        <v>60</v>
+      </c>
+      <c r="D710" s="1">
+        <v>8</v>
+      </c>
+      <c r="E710" s="1">
+        <v>9</v>
+      </c>
+      <c r="F710" s="1">
+        <v>0</v>
+      </c>
+      <c r="G710" s="2"/>
+      <c r="H710" s="1">
+        <v>9</v>
+      </c>
+      <c r="I710">
+        <f t="shared" si="11"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="711" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A711" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C711" s="1">
+        <v>60</v>
+      </c>
+      <c r="D711" s="1">
+        <v>8</v>
+      </c>
+      <c r="E711" s="1">
+        <v>7</v>
+      </c>
+      <c r="F711" s="1">
+        <v>0</v>
+      </c>
+      <c r="G711" s="2"/>
+      <c r="H711" s="1">
+        <v>6</v>
+      </c>
+      <c r="I711">
+        <f t="shared" si="11"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="712" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A712" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C712" s="1">
+        <v>60</v>
+      </c>
+      <c r="D712" s="1">
+        <v>6</v>
+      </c>
+      <c r="E712" s="1">
+        <v>3</v>
+      </c>
+      <c r="F712" s="1">
+        <v>0</v>
+      </c>
+      <c r="G712" s="2"/>
+      <c r="H712" s="1">
+        <v>8</v>
+      </c>
+      <c r="I712">
+        <f t="shared" si="11"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="713" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A713" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C713" s="1">
+        <v>60</v>
+      </c>
+      <c r="D713" s="1">
+        <v>6</v>
+      </c>
+      <c r="E713" s="1">
+        <v>5</v>
+      </c>
+      <c r="F713" s="1">
+        <v>1</v>
+      </c>
+      <c r="G713" s="2"/>
+      <c r="H713" s="1">
+        <v>3</v>
+      </c>
+      <c r="I713">
+        <f t="shared" si="11"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="714" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A714" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C714" s="1">
+        <v>60</v>
+      </c>
+      <c r="D714" s="1">
+        <v>8</v>
+      </c>
+      <c r="E714" s="1">
+        <v>9</v>
+      </c>
+      <c r="F714" s="1">
+        <v>0</v>
+      </c>
+      <c r="G714" s="2"/>
+      <c r="H714" s="1">
+        <v>5</v>
+      </c>
+      <c r="I714">
+        <f t="shared" si="11"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="715" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A715" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C715" s="1">
+        <v>60</v>
+      </c>
+      <c r="D715" s="1">
+        <v>8</v>
+      </c>
+      <c r="E715" s="1">
+        <v>6</v>
+      </c>
+      <c r="F715" s="1">
+        <v>3</v>
+      </c>
+      <c r="G715" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H715" s="1">
+        <v>7</v>
+      </c>
+      <c r="I715">
+        <f t="shared" si="11"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="716" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A716" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C716" s="1">
+        <v>60</v>
+      </c>
+      <c r="D716" s="1">
+        <v>8</v>
+      </c>
+      <c r="E716" s="1">
+        <v>8</v>
+      </c>
+      <c r="F716" s="1">
+        <v>3</v>
+      </c>
+      <c r="G716" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H716" s="1">
+        <v>6</v>
+      </c>
+      <c r="I716">
+        <f t="shared" si="11"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="717" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A717" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C717" s="1">
+        <v>60</v>
+      </c>
+      <c r="D717" s="1">
+        <v>7</v>
+      </c>
+      <c r="E717" s="1">
+        <v>5</v>
+      </c>
+      <c r="F717" s="1">
+        <v>5</v>
+      </c>
+      <c r="G717" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H717" s="1">
+        <v>2</v>
+      </c>
+      <c r="I717">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="718" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A718" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C718" s="1">
+        <v>60</v>
+      </c>
+      <c r="D718" s="1">
+        <v>5</v>
+      </c>
+      <c r="E718" s="1">
+        <v>5</v>
+      </c>
+      <c r="F718" s="1">
+        <v>0</v>
+      </c>
+      <c r="G718" s="2"/>
+      <c r="H718" s="1">
+        <v>4</v>
+      </c>
+      <c r="I718">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="719" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A719" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C719" s="1">
+        <v>60</v>
+      </c>
+      <c r="D719" s="1">
+        <v>7</v>
+      </c>
+      <c r="E719" s="1">
+        <v>4</v>
+      </c>
+      <c r="F719" s="1">
+        <v>0</v>
+      </c>
+      <c r="G719" s="2"/>
+      <c r="H719" s="1">
+        <v>7</v>
+      </c>
+      <c r="I719">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="720" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A720" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C720" s="1">
+        <v>60</v>
+      </c>
+      <c r="D720" s="1">
+        <v>7</v>
+      </c>
+      <c r="E720" s="1">
+        <v>6</v>
+      </c>
+      <c r="F720" s="1">
+        <v>4</v>
+      </c>
+      <c r="G720" s="2"/>
+      <c r="H720" s="1">
+        <v>6</v>
+      </c>
+      <c r="I720">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="721" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A721" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C721" s="1">
+        <v>60</v>
+      </c>
+      <c r="D721" s="1">
+        <v>7</v>
+      </c>
+      <c r="E721" s="1">
+        <v>6</v>
+      </c>
+      <c r="F721" s="1">
+        <v>5</v>
+      </c>
+      <c r="G721" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H721" s="1">
+        <v>8</v>
+      </c>
+      <c r="I721">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="722" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A722" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C722" s="1">
+        <v>60</v>
+      </c>
+      <c r="D722" s="1">
+        <v>8</v>
+      </c>
+      <c r="E722" s="1">
+        <v>7</v>
+      </c>
+      <c r="F722" s="1">
+        <v>0</v>
+      </c>
+      <c r="G722" s="2"/>
+      <c r="H722" s="1">
+        <v>6</v>
+      </c>
+      <c r="I722">
+        <f t="shared" si="11"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="723" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A723" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C723" s="1">
+        <v>60</v>
+      </c>
+      <c r="D723" s="1">
+        <v>7</v>
+      </c>
+      <c r="E723" s="1">
+        <v>6</v>
+      </c>
+      <c r="F723" s="1">
+        <v>1</v>
+      </c>
+      <c r="G723" s="2"/>
+      <c r="H723" s="1">
+        <v>5</v>
+      </c>
+      <c r="I723">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="724" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A724" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C724" s="1">
+        <v>60</v>
+      </c>
+      <c r="D724" s="1">
+        <v>7</v>
+      </c>
+      <c r="E724" s="1">
+        <v>8</v>
+      </c>
+      <c r="F724" s="1">
+        <v>0</v>
+      </c>
+      <c r="G724" s="2"/>
+      <c r="H724" s="1">
+        <v>10</v>
+      </c>
+      <c r="I724">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="725" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A725" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C725" s="1">
+        <v>60</v>
+      </c>
+      <c r="D725" s="1">
+        <v>5</v>
+      </c>
+      <c r="E725" s="1">
+        <v>3</v>
+      </c>
+      <c r="F725" s="1">
+        <v>0</v>
+      </c>
+      <c r="G725" s="2"/>
+      <c r="H725" s="1">
+        <v>9</v>
+      </c>
+      <c r="I725">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="726" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A726" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B726" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C726" s="1">
+        <v>60</v>
+      </c>
+      <c r="D726" s="1">
+        <v>6</v>
+      </c>
+      <c r="E726" s="1">
+        <v>5</v>
+      </c>
+      <c r="F726" s="1">
+        <v>0</v>
+      </c>
+      <c r="G726" s="2"/>
+      <c r="H726" s="1">
+        <v>9</v>
+      </c>
+      <c r="I726">
+        <f t="shared" si="11"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="727" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A727" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C727" s="1">
+        <v>60</v>
+      </c>
+      <c r="D727" s="1">
+        <v>7</v>
+      </c>
+      <c r="E727" s="1">
+        <v>8</v>
+      </c>
+      <c r="F727" s="1">
+        <v>0</v>
+      </c>
+      <c r="G727" s="2"/>
+      <c r="H727" s="1">
+        <v>6</v>
+      </c>
+      <c r="I727">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="728" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A728" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B728" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C728" s="1">
+        <v>60</v>
+      </c>
+      <c r="D728" s="1">
+        <v>6</v>
+      </c>
+      <c r="E728" s="1">
+        <v>6</v>
+      </c>
+      <c r="F728" s="1">
+        <v>5</v>
+      </c>
+      <c r="G728" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H728" s="1">
+        <v>8</v>
+      </c>
+      <c r="I728">
+        <f t="shared" si="11"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="729" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A729" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C729" s="1">
+        <v>60</v>
+      </c>
+      <c r="D729" s="1">
+        <v>7</v>
+      </c>
+      <c r="E729" s="1">
+        <v>7</v>
+      </c>
+      <c r="F729" s="1">
+        <v>0</v>
+      </c>
+      <c r="G729" s="2"/>
+      <c r="H729" s="1">
+        <v>7</v>
+      </c>
+      <c r="I729">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="730" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A730" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C730" s="1">
+        <v>60</v>
+      </c>
+      <c r="D730" s="1">
+        <v>5</v>
+      </c>
+      <c r="E730" s="1">
+        <v>3</v>
+      </c>
+      <c r="F730" s="1">
+        <v>0</v>
+      </c>
+      <c r="G730" s="2"/>
+      <c r="H730" s="1">
+        <v>5</v>
+      </c>
+      <c r="I730">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="731" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A731" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C731" s="1">
+        <v>60</v>
+      </c>
+      <c r="D731" s="1">
+        <v>4</v>
+      </c>
+      <c r="E731" s="1">
+        <v>3</v>
+      </c>
+      <c r="F731" s="1">
+        <v>0</v>
+      </c>
+      <c r="G731" s="2"/>
+      <c r="H731" s="1">
+        <v>7</v>
+      </c>
+      <c r="I731">
+        <f t="shared" si="11"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="732" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A732" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C732" s="1">
+        <v>60</v>
+      </c>
+      <c r="D732" s="1">
+        <v>7</v>
+      </c>
+      <c r="E732" s="1">
+        <v>8</v>
+      </c>
+      <c r="F732" s="1">
+        <v>0</v>
+      </c>
+      <c r="G732" s="2"/>
+      <c r="H732" s="1">
+        <v>7</v>
+      </c>
+      <c r="I732">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="733" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A733" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C733" s="1">
+        <v>60</v>
+      </c>
+      <c r="D733" s="1">
+        <v>6</v>
+      </c>
+      <c r="E733" s="1">
+        <v>2</v>
+      </c>
+      <c r="F733" s="1">
+        <v>0</v>
+      </c>
+      <c r="G733" s="2"/>
+      <c r="H733" s="1">
+        <v>5</v>
+      </c>
+      <c r="I733">
+        <f t="shared" si="11"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="734" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A734" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B734" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C734" s="1">
+        <v>60</v>
+      </c>
+      <c r="D734" s="1">
+        <v>3</v>
+      </c>
+      <c r="E734" s="1">
+        <v>5</v>
+      </c>
+      <c r="F734" s="1">
+        <v>0</v>
+      </c>
+      <c r="G734" s="2"/>
+      <c r="H734" s="1">
+        <v>10</v>
+      </c>
+      <c r="I734">
+        <f t="shared" si="11"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="735" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A735" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C735" s="1">
+        <v>60</v>
+      </c>
+      <c r="D735" s="1">
+        <v>3</v>
+      </c>
+      <c r="E735" s="1">
+        <v>5</v>
+      </c>
+      <c r="F735" s="1">
+        <v>2</v>
+      </c>
+      <c r="G735" s="2"/>
+      <c r="H735" s="1">
+        <v>5</v>
+      </c>
+      <c r="I735">
+        <f t="shared" si="11"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="736" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A736" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C736" s="1">
+        <v>60</v>
+      </c>
+      <c r="D736" s="1">
+        <v>5</v>
+      </c>
+      <c r="E736" s="1">
+        <v>4</v>
+      </c>
+      <c r="F736" s="1">
+        <v>4</v>
+      </c>
+      <c r="G736" s="2"/>
+      <c r="H736" s="1">
+        <v>7</v>
+      </c>
+      <c r="I736">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="737" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A737" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C737" s="1">
+        <v>60</v>
+      </c>
+      <c r="D737" s="1">
+        <v>5</v>
+      </c>
+      <c r="E737" s="1">
+        <v>5</v>
+      </c>
+      <c r="F737" s="1">
+        <v>3</v>
+      </c>
+      <c r="G737" s="2"/>
+      <c r="H737" s="1">
+        <v>5</v>
+      </c>
+      <c r="I737">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="738" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A738" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C738" s="1">
+        <v>60</v>
+      </c>
+      <c r="D738" s="1">
+        <v>6</v>
+      </c>
+      <c r="E738" s="1">
+        <v>1</v>
+      </c>
+      <c r="F738" s="1">
+        <v>0</v>
+      </c>
+      <c r="G738" s="2"/>
+      <c r="H738" s="1">
+        <v>7</v>
+      </c>
+      <c r="I738">
+        <f t="shared" si="11"/>
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Wellness.xlsx
+++ b/data/2026-2027/Wellness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D449821D-AA8F-E548-8A0B-6EC7B6D5530A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5194D532-A040-0A4E-8154-B982888AA8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="116">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -369,6 +369,21 @@
   </si>
   <si>
     <t>Ampoule</t>
+  </si>
+  <si>
+    <t>Genoux gauche</t>
+  </si>
+  <si>
+    <t>Psoas gauche </t>
+  </si>
+  <si>
+    <t>Hanche</t>
+  </si>
+  <si>
+    <t>Qudriceps </t>
+  </si>
+  <si>
+    <t>Cheville mollet </t>
   </si>
 </sst>
 </file>
@@ -755,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:J738"/>
+  <dimension ref="A1:J784"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -21329,7 +21344,7 @@
         <v>7</v>
       </c>
       <c r="I707">
-        <f t="shared" ref="I707:I738" si="11">C707*D707</f>
+        <f t="shared" ref="I707:I770" si="11">C707*D707</f>
         <v>100</v>
       </c>
     </row>
@@ -22209,6 +22224,1310 @@
       <c r="I738">
         <f t="shared" si="11"/>
         <v>360</v>
+      </c>
+    </row>
+    <row r="739" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A739" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B739" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C739" s="1">
+        <v>50</v>
+      </c>
+      <c r="D739" s="1">
+        <v>4</v>
+      </c>
+      <c r="E739" s="1">
+        <v>4</v>
+      </c>
+      <c r="F739" s="1">
+        <v>0</v>
+      </c>
+      <c r="G739" s="2"/>
+      <c r="H739" s="1">
+        <v>2</v>
+      </c>
+      <c r="I739">
+        <f t="shared" si="11"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="740" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A740" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B740" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C740" s="1">
+        <v>50</v>
+      </c>
+      <c r="D740" s="1">
+        <v>7</v>
+      </c>
+      <c r="E740" s="1">
+        <v>7</v>
+      </c>
+      <c r="F740" s="1">
+        <v>0</v>
+      </c>
+      <c r="G740" s="2"/>
+      <c r="H740" s="1">
+        <v>8</v>
+      </c>
+      <c r="I740">
+        <f t="shared" si="11"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="741" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A741" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B741" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C741" s="1">
+        <v>50</v>
+      </c>
+      <c r="D741" s="1">
+        <v>3</v>
+      </c>
+      <c r="E741" s="1">
+        <v>0</v>
+      </c>
+      <c r="F741" s="1">
+        <v>0</v>
+      </c>
+      <c r="G741" s="2"/>
+      <c r="H741" s="1">
+        <v>10</v>
+      </c>
+      <c r="I741">
+        <f t="shared" si="11"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="742" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A742" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B742" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C742" s="1">
+        <v>50</v>
+      </c>
+      <c r="D742" s="1">
+        <v>4</v>
+      </c>
+      <c r="E742" s="1">
+        <v>4</v>
+      </c>
+      <c r="F742" s="1">
+        <v>1</v>
+      </c>
+      <c r="G742" s="2"/>
+      <c r="H742" s="1">
+        <v>4</v>
+      </c>
+      <c r="I742">
+        <f t="shared" si="11"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="743" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A743" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B743" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C743" s="1">
+        <v>50</v>
+      </c>
+      <c r="D743" s="1">
+        <v>4</v>
+      </c>
+      <c r="E743" s="1">
+        <v>4</v>
+      </c>
+      <c r="F743" s="1">
+        <v>3</v>
+      </c>
+      <c r="G743" s="2"/>
+      <c r="H743" s="1">
+        <v>6</v>
+      </c>
+      <c r="I743">
+        <f t="shared" si="11"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="744" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A744" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B744" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C744" s="1">
+        <v>50</v>
+      </c>
+      <c r="D744" s="1">
+        <v>5</v>
+      </c>
+      <c r="E744" s="1">
+        <v>5</v>
+      </c>
+      <c r="F744" s="1">
+        <v>0</v>
+      </c>
+      <c r="G744" s="2"/>
+      <c r="H744" s="1">
+        <v>6</v>
+      </c>
+      <c r="I744">
+        <f t="shared" si="11"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="745" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A745" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B745" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C745" s="1">
+        <v>50</v>
+      </c>
+      <c r="D745" s="1">
+        <v>6</v>
+      </c>
+      <c r="E745" s="1">
+        <v>5</v>
+      </c>
+      <c r="F745" s="1">
+        <v>0</v>
+      </c>
+      <c r="G745" s="2"/>
+      <c r="H745" s="1">
+        <v>10</v>
+      </c>
+      <c r="I745">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="746" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A746" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B746" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C746" s="1">
+        <v>50</v>
+      </c>
+      <c r="D746" s="1">
+        <v>3</v>
+      </c>
+      <c r="E746" s="1">
+        <v>3</v>
+      </c>
+      <c r="F746" s="1">
+        <v>1</v>
+      </c>
+      <c r="G746" s="2"/>
+      <c r="H746" s="1">
+        <v>6</v>
+      </c>
+      <c r="I746">
+        <f t="shared" si="11"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="747" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A747" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B747" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C747" s="1">
+        <v>50</v>
+      </c>
+      <c r="D747" s="1">
+        <v>7</v>
+      </c>
+      <c r="E747" s="1">
+        <v>6</v>
+      </c>
+      <c r="F747" s="1">
+        <v>0</v>
+      </c>
+      <c r="G747" s="2"/>
+      <c r="H747" s="1">
+        <v>7</v>
+      </c>
+      <c r="I747">
+        <f t="shared" si="11"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="748" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A748" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B748" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C748" s="1">
+        <v>50</v>
+      </c>
+      <c r="D748" s="1">
+        <v>5</v>
+      </c>
+      <c r="E748" s="1">
+        <v>5</v>
+      </c>
+      <c r="F748" s="1">
+        <v>4</v>
+      </c>
+      <c r="G748" s="2"/>
+      <c r="H748" s="1">
+        <v>6</v>
+      </c>
+      <c r="I748">
+        <f t="shared" si="11"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="749" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A749" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B749" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C749" s="1">
+        <v>50</v>
+      </c>
+      <c r="D749" s="1">
+        <v>7</v>
+      </c>
+      <c r="E749" s="1">
+        <v>7</v>
+      </c>
+      <c r="F749" s="1">
+        <v>3</v>
+      </c>
+      <c r="G749" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H749" s="1">
+        <v>5</v>
+      </c>
+      <c r="I749">
+        <f t="shared" si="11"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="750" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A750" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B750" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C750" s="1">
+        <v>50</v>
+      </c>
+      <c r="D750" s="1">
+        <v>5</v>
+      </c>
+      <c r="E750" s="1">
+        <v>2</v>
+      </c>
+      <c r="F750" s="1">
+        <v>0</v>
+      </c>
+      <c r="G750" s="2"/>
+      <c r="H750" s="1">
+        <v>10</v>
+      </c>
+      <c r="I750">
+        <f t="shared" si="11"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="751" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A751" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B751" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C751" s="1">
+        <v>50</v>
+      </c>
+      <c r="D751" s="1">
+        <v>4</v>
+      </c>
+      <c r="E751" s="1">
+        <v>3</v>
+      </c>
+      <c r="F751" s="1">
+        <v>0</v>
+      </c>
+      <c r="G751" s="2"/>
+      <c r="H751" s="1">
+        <v>6</v>
+      </c>
+      <c r="I751">
+        <f t="shared" si="11"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="752" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A752" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B752" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C752" s="1">
+        <v>50</v>
+      </c>
+      <c r="D752" s="1">
+        <v>7</v>
+      </c>
+      <c r="E752" s="1">
+        <v>8</v>
+      </c>
+      <c r="F752" s="1">
+        <v>0</v>
+      </c>
+      <c r="G752" s="2"/>
+      <c r="H752" s="1">
+        <v>8</v>
+      </c>
+      <c r="I752">
+        <f t="shared" si="11"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="753" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A753" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B753" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C753" s="1">
+        <v>50</v>
+      </c>
+      <c r="D753" s="1">
+        <v>6</v>
+      </c>
+      <c r="E753" s="1">
+        <v>4</v>
+      </c>
+      <c r="F753" s="1">
+        <v>0</v>
+      </c>
+      <c r="G753" s="2"/>
+      <c r="H753" s="1">
+        <v>6</v>
+      </c>
+      <c r="I753">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="754" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A754" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B754" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C754" s="1">
+        <v>50</v>
+      </c>
+      <c r="D754" s="1">
+        <v>3</v>
+      </c>
+      <c r="E754" s="1">
+        <v>3</v>
+      </c>
+      <c r="F754" s="1">
+        <v>1</v>
+      </c>
+      <c r="G754" s="2"/>
+      <c r="H754" s="1">
+        <v>4</v>
+      </c>
+      <c r="I754">
+        <f t="shared" si="11"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="755" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A755" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B755" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C755" s="1">
+        <v>50</v>
+      </c>
+      <c r="D755" s="1">
+        <v>5</v>
+      </c>
+      <c r="E755" s="1">
+        <v>3</v>
+      </c>
+      <c r="F755" s="1">
+        <v>3</v>
+      </c>
+      <c r="G755" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H755" s="1">
+        <v>8</v>
+      </c>
+      <c r="I755">
+        <f t="shared" si="11"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="756" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A756" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B756" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C756" s="1">
+        <v>50</v>
+      </c>
+      <c r="D756" s="1">
+        <v>5</v>
+      </c>
+      <c r="E756" s="1">
+        <v>1</v>
+      </c>
+      <c r="F756" s="1">
+        <v>0</v>
+      </c>
+      <c r="G756" s="2"/>
+      <c r="H756" s="1">
+        <v>10</v>
+      </c>
+      <c r="I756">
+        <f t="shared" si="11"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="757" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A757" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B757" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C757" s="1">
+        <v>50</v>
+      </c>
+      <c r="D757" s="1">
+        <v>8</v>
+      </c>
+      <c r="E757" s="1">
+        <v>7</v>
+      </c>
+      <c r="F757" s="1">
+        <v>6</v>
+      </c>
+      <c r="G757" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H757" s="1">
+        <v>8</v>
+      </c>
+      <c r="I757">
+        <f t="shared" si="11"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="758" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A758" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C758" s="1">
+        <v>50</v>
+      </c>
+      <c r="D758" s="1">
+        <v>5</v>
+      </c>
+      <c r="E758" s="1">
+        <v>5</v>
+      </c>
+      <c r="F758" s="1">
+        <v>0</v>
+      </c>
+      <c r="G758" s="2"/>
+      <c r="H758" s="1">
+        <v>9</v>
+      </c>
+      <c r="I758">
+        <f t="shared" si="11"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="759" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A759" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B759" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C759" s="1">
+        <v>50</v>
+      </c>
+      <c r="D759" s="1">
+        <v>3</v>
+      </c>
+      <c r="E759" s="1">
+        <v>4</v>
+      </c>
+      <c r="F759" s="1">
+        <v>0</v>
+      </c>
+      <c r="G759" s="2"/>
+      <c r="H759" s="1">
+        <v>9</v>
+      </c>
+      <c r="I759">
+        <f t="shared" si="11"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="760" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A760" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B760" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C760" s="1">
+        <v>50</v>
+      </c>
+      <c r="D760" s="1">
+        <v>2</v>
+      </c>
+      <c r="E760" s="1">
+        <v>4</v>
+      </c>
+      <c r="F760" s="1">
+        <v>0</v>
+      </c>
+      <c r="G760" s="2"/>
+      <c r="H760" s="1">
+        <v>8</v>
+      </c>
+      <c r="I760">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="761" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A761" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C761" s="1">
+        <v>60</v>
+      </c>
+      <c r="D761" s="1">
+        <v>7</v>
+      </c>
+      <c r="E761" s="1">
+        <v>8</v>
+      </c>
+      <c r="F761" s="1">
+        <v>0</v>
+      </c>
+      <c r="G761" s="2"/>
+      <c r="H761" s="1">
+        <v>7</v>
+      </c>
+      <c r="I761">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="762" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A762" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C762" s="1">
+        <v>60</v>
+      </c>
+      <c r="D762" s="1">
+        <v>5</v>
+      </c>
+      <c r="E762" s="1">
+        <v>7</v>
+      </c>
+      <c r="F762" s="1">
+        <v>6</v>
+      </c>
+      <c r="G762" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H762" s="1">
+        <v>8</v>
+      </c>
+      <c r="I762">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="763" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A763" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C763" s="1">
+        <v>60</v>
+      </c>
+      <c r="D763" s="1">
+        <v>6</v>
+      </c>
+      <c r="E763" s="1">
+        <v>5</v>
+      </c>
+      <c r="F763" s="1">
+        <v>0</v>
+      </c>
+      <c r="G763" s="2"/>
+      <c r="H763" s="1">
+        <v>6</v>
+      </c>
+      <c r="I763">
+        <f t="shared" si="11"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="764" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A764" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C764" s="1">
+        <v>60</v>
+      </c>
+      <c r="D764" s="1">
+        <v>6</v>
+      </c>
+      <c r="E764" s="1">
+        <v>4</v>
+      </c>
+      <c r="F764" s="1">
+        <v>2</v>
+      </c>
+      <c r="G764" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H764" s="1">
+        <v>6</v>
+      </c>
+      <c r="I764">
+        <f t="shared" si="11"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="765" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A765" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C765" s="1">
+        <v>60</v>
+      </c>
+      <c r="D765" s="1">
+        <v>5</v>
+      </c>
+      <c r="E765" s="1">
+        <v>6</v>
+      </c>
+      <c r="F765" s="1">
+        <v>7</v>
+      </c>
+      <c r="G765" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H765" s="1">
+        <v>4</v>
+      </c>
+      <c r="I765">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="766" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A766" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C766" s="1">
+        <v>60</v>
+      </c>
+      <c r="D766" s="1">
+        <v>7</v>
+      </c>
+      <c r="E766" s="1">
+        <v>6</v>
+      </c>
+      <c r="F766" s="1">
+        <v>1</v>
+      </c>
+      <c r="G766" s="2"/>
+      <c r="H766" s="1">
+        <v>8</v>
+      </c>
+      <c r="I766">
+        <f t="shared" si="11"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="767" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A767" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C767" s="1">
+        <v>60</v>
+      </c>
+      <c r="D767" s="1">
+        <v>8</v>
+      </c>
+      <c r="E767" s="1">
+        <v>8</v>
+      </c>
+      <c r="F767" s="1">
+        <v>0</v>
+      </c>
+      <c r="G767" s="2"/>
+      <c r="H767" s="1">
+        <v>2</v>
+      </c>
+      <c r="I767">
+        <f t="shared" si="11"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="768" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A768" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C768" s="1">
+        <v>60</v>
+      </c>
+      <c r="D768" s="1">
+        <v>6</v>
+      </c>
+      <c r="E768" s="1">
+        <v>5</v>
+      </c>
+      <c r="F768" s="1">
+        <v>1</v>
+      </c>
+      <c r="G768" s="2"/>
+      <c r="H768" s="1">
+        <v>5</v>
+      </c>
+      <c r="I768">
+        <f t="shared" si="11"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="769" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A769" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C769" s="1">
+        <v>60</v>
+      </c>
+      <c r="D769" s="1">
+        <v>6</v>
+      </c>
+      <c r="E769" s="1">
+        <v>6</v>
+      </c>
+      <c r="F769" s="1">
+        <v>0</v>
+      </c>
+      <c r="G769" s="2"/>
+      <c r="H769" s="1">
+        <v>4</v>
+      </c>
+      <c r="I769">
+        <f t="shared" si="11"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="770" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A770" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C770" s="1">
+        <v>60</v>
+      </c>
+      <c r="D770" s="1">
+        <v>6</v>
+      </c>
+      <c r="E770" s="1">
+        <v>5</v>
+      </c>
+      <c r="F770" s="1">
+        <v>4</v>
+      </c>
+      <c r="G770" s="2"/>
+      <c r="H770" s="1">
+        <v>7</v>
+      </c>
+      <c r="I770">
+        <f t="shared" si="11"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="771" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A771" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C771" s="1">
+        <v>60</v>
+      </c>
+      <c r="D771" s="1">
+        <v>6</v>
+      </c>
+      <c r="E771" s="1">
+        <v>6</v>
+      </c>
+      <c r="F771" s="1">
+        <v>0</v>
+      </c>
+      <c r="G771" s="2"/>
+      <c r="H771" s="1">
+        <v>4</v>
+      </c>
+      <c r="I771">
+        <f t="shared" ref="I771:I784" si="12">C771*D771</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="772" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A772" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C772" s="1">
+        <v>60</v>
+      </c>
+      <c r="D772" s="1">
+        <v>6</v>
+      </c>
+      <c r="E772" s="1">
+        <v>4</v>
+      </c>
+      <c r="F772" s="1">
+        <v>0</v>
+      </c>
+      <c r="G772" s="2"/>
+      <c r="H772" s="1">
+        <v>7</v>
+      </c>
+      <c r="I772">
+        <f t="shared" si="12"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="773" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A773" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B773" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C773" s="1">
+        <v>60</v>
+      </c>
+      <c r="D773" s="1">
+        <v>7</v>
+      </c>
+      <c r="E773" s="1">
+        <v>4</v>
+      </c>
+      <c r="F773" s="1">
+        <v>0</v>
+      </c>
+      <c r="G773" s="2"/>
+      <c r="H773" s="1">
+        <v>9</v>
+      </c>
+      <c r="I773">
+        <f t="shared" si="12"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="774" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A774" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C774" s="1">
+        <v>60</v>
+      </c>
+      <c r="D774" s="1">
+        <v>5</v>
+      </c>
+      <c r="E774" s="1">
+        <v>3</v>
+      </c>
+      <c r="F774" s="1">
+        <v>0</v>
+      </c>
+      <c r="G774" s="2"/>
+      <c r="H774" s="1">
+        <v>10</v>
+      </c>
+      <c r="I774">
+        <f t="shared" si="12"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="775" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A775" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C775" s="1">
+        <v>60</v>
+      </c>
+      <c r="D775" s="1">
+        <v>5</v>
+      </c>
+      <c r="E775" s="1">
+        <v>2</v>
+      </c>
+      <c r="F775" s="1">
+        <v>0</v>
+      </c>
+      <c r="G775" s="2"/>
+      <c r="H775" s="1">
+        <v>6</v>
+      </c>
+      <c r="I775">
+        <f t="shared" si="12"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="776" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A776" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C776" s="1">
+        <v>70</v>
+      </c>
+      <c r="D776" s="1">
+        <v>6</v>
+      </c>
+      <c r="E776" s="1">
+        <v>3</v>
+      </c>
+      <c r="F776" s="1">
+        <v>3</v>
+      </c>
+      <c r="G776" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H776" s="1">
+        <v>7</v>
+      </c>
+      <c r="I776">
+        <f t="shared" si="12"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="777" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A777" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C777" s="1">
+        <v>70</v>
+      </c>
+      <c r="D777" s="1">
+        <v>4</v>
+      </c>
+      <c r="E777" s="1">
+        <v>0</v>
+      </c>
+      <c r="F777" s="1">
+        <v>0</v>
+      </c>
+      <c r="G777" s="2"/>
+      <c r="H777" s="1">
+        <v>10</v>
+      </c>
+      <c r="I777">
+        <f t="shared" si="12"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="778" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A778" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C778" s="1">
+        <v>70</v>
+      </c>
+      <c r="D778" s="1">
+        <v>6</v>
+      </c>
+      <c r="E778" s="1">
+        <v>4</v>
+      </c>
+      <c r="F778" s="1">
+        <v>0</v>
+      </c>
+      <c r="G778" s="2"/>
+      <c r="H778" s="1">
+        <v>9</v>
+      </c>
+      <c r="I778">
+        <f t="shared" si="12"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="779" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A779" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C779" s="1">
+        <v>70</v>
+      </c>
+      <c r="D779" s="1">
+        <v>7</v>
+      </c>
+      <c r="E779" s="1">
+        <v>7</v>
+      </c>
+      <c r="F779" s="1">
+        <v>0</v>
+      </c>
+      <c r="G779" s="2"/>
+      <c r="H779" s="1">
+        <v>7</v>
+      </c>
+      <c r="I779">
+        <f t="shared" si="12"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="780" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A780" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B780" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C780" s="1">
+        <v>70</v>
+      </c>
+      <c r="D780" s="1">
+        <v>5</v>
+      </c>
+      <c r="E780" s="1">
+        <v>4</v>
+      </c>
+      <c r="F780" s="1">
+        <v>0</v>
+      </c>
+      <c r="G780" s="2"/>
+      <c r="H780" s="1">
+        <v>6</v>
+      </c>
+      <c r="I780">
+        <f t="shared" si="12"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="781" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A781" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B781" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C781" s="1">
+        <v>70</v>
+      </c>
+      <c r="D781" s="1">
+        <v>7</v>
+      </c>
+      <c r="E781" s="1">
+        <v>8</v>
+      </c>
+      <c r="F781" s="1">
+        <v>0</v>
+      </c>
+      <c r="G781" s="2"/>
+      <c r="H781" s="1">
+        <v>6</v>
+      </c>
+      <c r="I781">
+        <f t="shared" si="12"/>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="782" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A782" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C782" s="1">
+        <v>70</v>
+      </c>
+      <c r="D782" s="1">
+        <v>6</v>
+      </c>
+      <c r="E782" s="1">
+        <v>5</v>
+      </c>
+      <c r="F782" s="1">
+        <v>6</v>
+      </c>
+      <c r="G782" s="2"/>
+      <c r="H782" s="1">
+        <v>6</v>
+      </c>
+      <c r="I782">
+        <f t="shared" si="12"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="783" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A783" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C783" s="1">
+        <v>70</v>
+      </c>
+      <c r="D783" s="1">
+        <v>6</v>
+      </c>
+      <c r="E783" s="1">
+        <v>4</v>
+      </c>
+      <c r="F783" s="1">
+        <v>5</v>
+      </c>
+      <c r="G783" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H783" s="1">
+        <v>7</v>
+      </c>
+      <c r="I783">
+        <f t="shared" si="12"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="784" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A784" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B784" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C784" s="1">
+        <v>70</v>
+      </c>
+      <c r="D784" s="1">
+        <v>7</v>
+      </c>
+      <c r="E784" s="1">
+        <v>7</v>
+      </c>
+      <c r="F784" s="1">
+        <v>5</v>
+      </c>
+      <c r="G784" s="2"/>
+      <c r="H784" s="1">
+        <v>7</v>
+      </c>
+      <c r="I784">
+        <f t="shared" si="12"/>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
